--- a/SQExcel.Portal/src/content/docs/ja/docs/images/medium-scale/メインDB_サービスマスター(blank).xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/medium-scale/メインDB_サービスマスター(blank).xlsx
@@ -79,163 +79,169 @@
     <x:t>項目名</x:t>
   </x:si>
   <x:si>
+    <x:t>service_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>service_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ad_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>banner_size</x:t>
+  </x:si>
+  <x:si>
+    <x:t>html_embed_available</x:t>
+  </x:si>
+  <x:si>
+    <x:t>js_embed_available</x:t>
+  </x:si>
+  <x:si>
+    <x:t>video_duration_sec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>price_weekly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>price_monthly</x:t>
+  </x:si>
+  <x:si>
+    <x:t>currency_code</x:t>
+  </x:si>
+  <x:si>
+    <x:t>start_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>end_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>is_active</x:t>
+  </x:si>
+  <x:si>
+    <x:t>created_at</x:t>
+  </x:si>
+  <x:si>
+    <x:t>created_by</x:t>
+  </x:si>
+  <x:si>
+    <x:t>updated_at</x:t>
+  </x:si>
+  <x:si>
+    <x:t>updated_by</x:t>
+  </x:si>
+  <x:si>
+    <x:t>処理成否</x:t>
+  </x:si>
+  <x:si>
+    <x:t>処理失敗時メッセージ</x:t>
+  </x:si>
+  <x:si>
     <x:t>項目論理名</x:t>
   </x:si>
   <x:si>
+    <x:t>サービスID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>サービス名</x:t>
+  </x:si>
+  <x:si>
+    <x:t>広告種別（B=バナー広告,V=動画広告）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>バナーサイズ（バナー広告のみ。例:468x60,728x90,300x250）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTML埋め込み可否（バナー広告のみ）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JavaScript埋め込み可否（バナー広告のみ）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>動画表示時間（秒）（動画広告のみ）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>週単位料金（税抜）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>月単位料金（税抜）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>料金通貨コード（ISO 4217）</x:t>
+  </x:si>
+  <x:si>
+    <x:t>適用開始日時</x:t>
+  </x:si>
+  <x:si>
+    <x:t>適用終了日時</x:t>
+  </x:si>
+  <x:si>
+    <x:t>有効フラグ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作成日時</x:t>
+  </x:si>
+  <x:si>
+    <x:t>作成者ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>更新日時</x:t>
+  </x:si>
+  <x:si>
+    <x:t>更新者ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>データ型</x:t>
   </x:si>
   <x:si>
+    <x:t>Char(8)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NVarChar(200)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Char(1)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VarChar(20)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bit</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Decimal(15,2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Char(3)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DateTime</x:t>
+  </x:si>
+  <x:si>
     <x:t>項目属性</x:t>
   </x:si>
   <x:si>
+    <x:t>K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D</x:t>
+  </x:si>
+  <x:si>
     <x:t>入力対象</x:t>
   </x:si>
   <x:si>
-    <x:t>service_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>サービスID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Char(8)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>K</x:t>
-  </x:si>
-  <x:si>
     <x:t>*</x:t>
   </x:si>
   <x:si>
-    <x:t>service_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>サービス名</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NVarChar(200)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ad_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>広告種別（B=バナー広告,V=動画広告）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Char(1)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>banner_size</x:t>
-  </x:si>
-  <x:si>
-    <x:t>バナーサイズ（バナー広告のみ。例:468x60,728x90,300x250）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VarChar(20)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>html_embed_available</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTML埋め込み可否（バナー広告のみ）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bit</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D</x:t>
-  </x:si>
-  <x:si>
-    <x:t>js_embed_available</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JavaScript埋め込み可否（バナー広告のみ）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>video_duration_sec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>動画表示時間（秒）（動画広告のみ）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>price_weekly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>週単位料金（税抜）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Decimal(15,2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>price_monthly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>月単位料金（税抜）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>currency_code</x:t>
-  </x:si>
-  <x:si>
-    <x:t>料金通貨コード（ISO 4217）</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Char(3)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>start_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>適用開始日時</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DateTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>end_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>適用終了日時</x:t>
-  </x:si>
-  <x:si>
-    <x:t>is_active</x:t>
-  </x:si>
-  <x:si>
-    <x:t>有効フラグ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>created_at</x:t>
-  </x:si>
-  <x:si>
-    <x:t>作成日時</x:t>
-  </x:si>
-  <x:si>
-    <x:t>created_by</x:t>
-  </x:si>
-  <x:si>
-    <x:t>作成者ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>updated_at</x:t>
-  </x:si>
-  <x:si>
-    <x:t>更新日時</x:t>
-  </x:si>
-  <x:si>
-    <x:t>updated_by</x:t>
-  </x:si>
-  <x:si>
-    <x:t>更新者ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>処理成否</x:t>
-  </x:si>
-  <x:si>
-    <x:t>処理失敗時メッセージ</x:t>
+    <x:t>DB種類</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Microsoft SQL Server</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -310,7 +316,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -389,8 +395,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -522,6 +531,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="0" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -853,15 +866,15 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:T10"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="21" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="18.710625" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="24.710625" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="18.710625" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="16.710625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="30.710625" style="2" customWidth="1"/>
-    <x:col min="6" max="8" width="14.710625" style="3" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="3" customWidth="1"/>
+    <x:col min="7" max="8" width="14.710625" style="3" customWidth="1"/>
     <x:col min="9" max="10" width="28.710625" style="4" customWidth="1"/>
     <x:col min="11" max="11" width="16.710625" style="2" customWidth="1"/>
     <x:col min="12" max="13" width="22.710625" style="5" customWidth="1"/>
@@ -872,6 +885,7 @@
     <x:col min="18" max="18" width="30.710625" style="2" customWidth="1"/>
     <x:col min="19" max="19" width="10.710625" style="1" customWidth="1"/>
     <x:col min="20" max="20" width="48.710625" style="1" customWidth="1"/>
+    <x:col min="21" max="16384" width="9.140625" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:20" s="6" customFormat="1">
@@ -887,8 +901,12 @@
       <x:c r="D1" s="8" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="10"/>
-      <x:c r="F1" s="11"/>
+      <x:c r="E1" s="9" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F1" s="33" t="s">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="G1" s="11"/>
       <x:c r="H1" s="11"/>
       <x:c r="I1" s="12"/>
@@ -931,185 +949,185 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C3" s="17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D3" s="17" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="17" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="18" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C3" s="17" t="s">
+      <x:c r="G3" s="18" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H3" s="18" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I3" s="19" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J3" s="19" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K3" s="17" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D3" s="17" t="s">
+      <x:c r="L3" s="20" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M3" s="20" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N3" s="18" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E3" s="17" t="s">
+      <x:c r="O3" s="20" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P3" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="Q3" s="20" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="F3" s="18" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G3" s="18" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H3" s="18" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I3" s="19" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="J3" s="19" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="K3" s="17" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L3" s="20" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="M3" s="20" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N3" s="18" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="O3" s="20" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="P3" s="17" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="Q3" s="20" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="R3" s="17" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="S3" s="21" t="s">
-        <x:v>58</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="T3" s="21" t="s">
-        <x:v>59</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:20" s="6" customFormat="1">
       <x:c r="A4" s="15" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="16" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="17" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="17" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E4" s="17" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F4" s="22" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G4" s="22" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H4" s="22" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="I4" s="23" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J4" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="K4" s="17" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="J4" s="23" t="s">
+      <x:c r="L4" s="24" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M4" s="24" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N4" s="22" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K4" s="17" t="s">
+      <x:c r="O4" s="24" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="P4" s="17" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="L4" s="24" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="M4" s="24" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N4" s="22" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="O4" s="24" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="P4" s="17" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="Q4" s="24" t="s">
-        <x:v>55</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="R4" s="17" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="S4" s="25"/>
       <x:c r="T4" s="25"/>
     </x:row>
     <x:row r="5" spans="1:20" s="6" customFormat="1">
       <x:c r="A5" s="15" t="s">
-        <x:v>8</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B5" s="16" t="s">
-        <x:v>13</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C5" s="17" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D5" s="17" t="s">
-        <x:v>21</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E5" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F5" s="18" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G5" s="18" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H5" s="18" t="s">
-        <x:v>34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I5" s="19" t="s">
-        <x:v>37</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="19" t="s">
-        <x:v>37</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K5" s="17" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="L5" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M5" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N5" s="18" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O5" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P5" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q5" s="20" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="R5" s="17" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="S5" s="25"/>
       <x:c r="T5" s="25"/>
     </x:row>
     <x:row r="6" spans="1:20" s="6" customFormat="1">
       <x:c r="A6" s="7" t="s">
-        <x:v>9</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B6" s="16" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C6" s="17" t="s">
         <x:v>5</x:v>
@@ -1118,43 +1136,43 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="17" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F6" s="18" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G6" s="18" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="18" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I6" s="19" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J6" s="19" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K6" s="17" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L6" s="20" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M6" s="20" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N6" s="18" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="O6" s="20" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="P6" s="17" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q6" s="20" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R6" s="17" t="s">
         <x:v>5</x:v>
@@ -1164,58 +1182,58 @@
     </x:row>
     <x:row r="7" spans="1:20">
       <x:c r="A7" s="26" t="s">
-        <x:v>10</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" s="27" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C7" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D7" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E7" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F7" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G7" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I7" s="30" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J7" s="30" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K7" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L7" s="31" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M7" s="31" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N7" s="29" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O7" s="31" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="P7" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q7" s="31" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R7" s="28" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S7" s="32"/>
       <x:c r="T7" s="32"/>
